--- a/output/optimisation_chantiers.xlsx
+++ b/output/optimisation_chantiers.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +33,15 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +51,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -73,12 +87,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,33 +529,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>562.8</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>499.77</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>499.77</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n"/>
+      <c r="B5" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>774.4</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>629.73</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>629.73</v>
+      </c>
+      <c r="I5" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
